--- a/artfynd/A 2365-2023 artfynd.xlsx
+++ b/artfynd/A 2365-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2365-2023 artfynd.xlsx
+++ b/artfynd/A 2365-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6549,10 +6549,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119265167</v>
+        <v>119265112</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6565,21 +6565,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>602800</v>
+        <v>602877</v>
       </c>
       <c r="R54" t="n">
-        <v>7030530</v>
+        <v>7030599</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6625,6 +6625,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6651,10 +6656,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119265112</v>
+        <v>119265171</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6667,21 +6672,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>602877</v>
+        <v>602879</v>
       </c>
       <c r="R55" t="n">
-        <v>7030599</v>
+        <v>7030592</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6727,11 +6732,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6758,10 +6758,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119265171</v>
+        <v>119265100</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>95455</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6774,21 +6774,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6798,10 +6798,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>602879</v>
+        <v>602722</v>
       </c>
       <c r="R56" t="n">
-        <v>7030592</v>
+        <v>7030672</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6860,10 +6860,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119265100</v>
+        <v>119265118</v>
       </c>
       <c r="B57" t="n">
-        <v>95455</v>
+        <v>90846</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6876,21 +6876,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>602722</v>
+        <v>602790</v>
       </c>
       <c r="R57" t="n">
-        <v>7030672</v>
+        <v>7030560</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119265118</v>
+        <v>119265111</v>
       </c>
       <c r="B58" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602790</v>
+        <v>602768</v>
       </c>
       <c r="R58" t="n">
-        <v>7030560</v>
+        <v>7030643</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119265111</v>
+        <v>119265168</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602768</v>
+        <v>602795</v>
       </c>
       <c r="R59" t="n">
-        <v>7030643</v>
+        <v>7030539</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119265168</v>
+        <v>119265116</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7178,25 +7178,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602795</v>
+        <v>602751</v>
       </c>
       <c r="R60" t="n">
-        <v>7030539</v>
+        <v>7030699</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7265,108 +7265,6 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>119265116</v>
-      </c>
-      <c r="B61" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Håssjöberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>602751</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7030699</v>
-      </c>
-      <c r="S61" t="n">
-        <v>25</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
